--- a/design/tables/Map.xlsx
+++ b/design/tables/Map.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Map" sheetId="1" r:id="R2bd21aad1510472a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Map" sheetId="1" r:id="R690b9b70cdbf4e22"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -484,6 +484,14 @@
         <x:v>midnight</x:v>
       </x:c>
     </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>midnight</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/Map.xlsx
+++ b/design/tables/Map.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Map" sheetId="1" r:id="R690b9b70cdbf4e22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Map" sheetId="1" r:id="R16e1a3f85c7b4d75"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -32,8 +32,19 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -50,6 +61,16 @@
         <x:fgColor rgb="FF34564C"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EEE9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF35584D"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -57,7 +78,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -78,6 +99,11 @@
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -282,6 +308,9 @@
   <x:cols>
     <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="48" customHeight="1">
@@ -291,6 +320,15 @@
       <x:c r="B1" s="6" t="str">
         <x:v>主题键</x:v>
       </x:c>
+      <x:c r="C1" s="9" t="str">
+        <x:v>格位网格间距</x:v>
+      </x:c>
+      <x:c r="D1" s="9" t="str">
+        <x:v>格位网格原点X</x:v>
+      </x:c>
+      <x:c r="E1" s="9" t="str">
+        <x:v>格位网格原点Y</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
@@ -299,6 +337,15 @@
       <x:c r="B2" s="3" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -307,6 +354,15 @@
       <x:c r="B3" s="3" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="C3" s="9" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="E3" s="9" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -315,6 +371,15 @@
       <x:c r="B4" s="6" t="str">
         <x:v>主题键</x:v>
       </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>格位网格间距</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="str">
+        <x:v>格位网格原点X</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="str">
+        <x:v>格位网格原点Y</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -323,6 +388,15 @@
       <x:c r="B5" s="5" t="str">
         <x:v>theme</x:v>
       </x:c>
+      <x:c r="C5" s="12" t="str">
+        <x:v>gridSize</x:v>
+      </x:c>
+      <x:c r="D5" s="12" t="str">
+        <x:v>gridOriginX</x:v>
+      </x:c>
+      <x:c r="E5" s="12" t="str">
+        <x:v>gridOriginY</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="n">
@@ -331,6 +405,15 @@
       <x:c r="B6" s="2" t="str">
         <x:v>courtyard</x:v>
       </x:c>
+      <x:c r="C6" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E6" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="7" t="n">
@@ -339,6 +422,15 @@
       <x:c r="B7" s="2" t="str">
         <x:v>courtyard</x:v>
       </x:c>
+      <x:c r="C7" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E7" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="7" t="n">
@@ -347,6 +439,15 @@
       <x:c r="B8" s="2" t="str">
         <x:v>courtyard</x:v>
       </x:c>
+      <x:c r="C8" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E8" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="7" t="n">
@@ -355,6 +456,15 @@
       <x:c r="B9" s="2" t="str">
         <x:v>courtyard</x:v>
       </x:c>
+      <x:c r="C9" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E9" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="7" t="n">
@@ -363,6 +473,15 @@
       <x:c r="B10" s="2" t="str">
         <x:v>courtyard</x:v>
       </x:c>
+      <x:c r="C10" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E10" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="7" t="n">
@@ -371,6 +490,15 @@
       <x:c r="B11" s="2" t="str">
         <x:v>rain</x:v>
       </x:c>
+      <x:c r="C11" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E11" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="7" t="n">
@@ -379,6 +507,15 @@
       <x:c r="B12" s="2" t="str">
         <x:v>rain</x:v>
       </x:c>
+      <x:c r="C12" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D12" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E12" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="7" t="n">
@@ -387,6 +524,15 @@
       <x:c r="B13" s="2" t="str">
         <x:v>rain</x:v>
       </x:c>
+      <x:c r="C13" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D13" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E13" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="7" t="n">
@@ -395,6 +541,15 @@
       <x:c r="B14" s="2" t="str">
         <x:v>rain</x:v>
       </x:c>
+      <x:c r="C14" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E14" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="7" t="n">
@@ -403,6 +558,15 @@
       <x:c r="B15" s="2" t="str">
         <x:v>rain</x:v>
       </x:c>
+      <x:c r="C15" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D15" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="7" t="n">
@@ -411,6 +575,15 @@
       <x:c r="B16" s="2" t="str">
         <x:v>market</x:v>
       </x:c>
+      <x:c r="C16" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E16" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="7" t="n">
@@ -419,6 +592,15 @@
       <x:c r="B17" s="2" t="str">
         <x:v>market</x:v>
       </x:c>
+      <x:c r="C17" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D17" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E17" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="7" t="n">
@@ -427,6 +609,15 @@
       <x:c r="B18" s="2" t="str">
         <x:v>market</x:v>
       </x:c>
+      <x:c r="C18" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D18" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E18" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="7" t="n">
@@ -435,6 +626,15 @@
       <x:c r="B19" s="2" t="str">
         <x:v>market</x:v>
       </x:c>
+      <x:c r="C19" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D19" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E19" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="7" t="n">
@@ -443,6 +643,15 @@
       <x:c r="B20" s="2" t="str">
         <x:v>market</x:v>
       </x:c>
+      <x:c r="C20" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D20" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E20" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="7" t="n">
@@ -451,6 +660,15 @@
       <x:c r="B21" s="2" t="str">
         <x:v>midnight</x:v>
       </x:c>
+      <x:c r="C21" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D21" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E21" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="7" t="n">
@@ -459,6 +677,15 @@
       <x:c r="B22" s="2" t="str">
         <x:v>midnight</x:v>
       </x:c>
+      <x:c r="C22" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D22" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E22" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="7" t="n">
@@ -467,6 +694,15 @@
       <x:c r="B23" s="2" t="str">
         <x:v>midnight</x:v>
       </x:c>
+      <x:c r="C23" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D23" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E23" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="7" t="n">
@@ -475,6 +711,15 @@
       <x:c r="B24" s="2" t="str">
         <x:v>midnight</x:v>
       </x:c>
+      <x:c r="C24" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D24" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E24" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="7" t="n">
@@ -483,6 +728,15 @@
       <x:c r="B25" s="2" t="str">
         <x:v>midnight</x:v>
       </x:c>
+      <x:c r="C25" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D25" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E25" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="n">
@@ -490,6 +744,15 @@
       </x:c>
       <x:c r="B26" t="str">
         <x:v>midnight</x:v>
+      </x:c>
+      <x:c r="C26" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D26" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E26" s="8" t="n">
+        <x:v>135</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/design/tables/Map.xlsx
+++ b/design/tables/Map.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Map" sheetId="1" r:id="R16e1a3f85c7b4d75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Map" sheetId="1" r:id="R5fa295e361824f77"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -755,6 +755,176 @@
         <x:v>135</x:v>
       </x:c>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B27" s="2" t="str">
+        <x:v>market</x:v>
+      </x:c>
+      <x:c r="C27" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D27" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E27" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="7" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B28" s="2" t="str">
+        <x:v>market</x:v>
+      </x:c>
+      <x:c r="C28" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D28" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E28" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="7" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B29" s="2" t="str">
+        <x:v>market</x:v>
+      </x:c>
+      <x:c r="C29" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D29" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E29" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B30" s="2" t="str">
+        <x:v>market</x:v>
+      </x:c>
+      <x:c r="C30" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D30" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E30" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="7" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B31" s="2" t="str">
+        <x:v>market</x:v>
+      </x:c>
+      <x:c r="C31" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D31" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E31" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="7" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B32" s="2" t="str">
+        <x:v>midnight</x:v>
+      </x:c>
+      <x:c r="C32" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D32" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E32" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="7" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B33" s="2" t="str">
+        <x:v>midnight</x:v>
+      </x:c>
+      <x:c r="C33" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D33" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E33" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="7" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B34" s="2" t="str">
+        <x:v>midnight</x:v>
+      </x:c>
+      <x:c r="C34" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D34" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E34" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B35" s="2" t="str">
+        <x:v>midnight</x:v>
+      </x:c>
+      <x:c r="C35" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D35" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E35" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B36" s="2" t="str">
+        <x:v>midnight</x:v>
+      </x:c>
+      <x:c r="C36" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D36" s="8" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E36" s="8" t="n">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
